--- a/kirill/outputs/2026-09-14-sales-comparison-2025-vs-2026.xlsx
+++ b/kirill/outputs/2026-09-14-sales-comparison-2025-vs-2026.xlsx
@@ -28,7 +28,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="C7" authorId="0">
+    <comment ref="B7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -41,7 +41,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C8" authorId="0">
+    <comment ref="B8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -53,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C9" authorId="0">
+    <comment ref="B9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -65,7 +65,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C10" authorId="0">
+    <comment ref="B10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -78,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C11" authorId="0">
+    <comment ref="B11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -90,7 +90,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0">
+    <comment ref="B12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -102,7 +102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C13" authorId="0">
+    <comment ref="B13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -114,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C14" authorId="0">
+    <comment ref="B14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -126,7 +126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C15" authorId="0">
+    <comment ref="B15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -138,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C16" authorId="0">
+    <comment ref="B16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -151,7 +151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C17" authorId="0">
+    <comment ref="B17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -163,7 +163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C18" authorId="0">
+    <comment ref="B18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -175,7 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C19" authorId="0">
+    <comment ref="B19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -187,7 +187,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C20" authorId="0">
+    <comment ref="B20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -199,7 +199,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C21" authorId="0">
+    <comment ref="B21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -211,7 +211,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C23" authorId="0">
+    <comment ref="B23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -223,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C25" authorId="0">
+    <comment ref="B25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -235,7 +235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C32" authorId="0">
+    <comment ref="B32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -247,7 +247,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C33" authorId="0">
+    <comment ref="B33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -264,7 +264,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="230">
   <si>
     <t xml:space="preserve">Sales Comparison 2025 vs 2026 - by Product CODE</t>
   </si>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">Calculation date:</t>
   </si>
   <si>
-    <t xml:space="preserve">Source: sales_analysis_20256.xlsx (sheets "2025" and "2026"), single customer: 160136 SEVEN GEAR FINLAND OY. Aggregated by product CODE; sorted by the absolute size of the change in EUR amount (largest to smallest).</t>
+    <t xml:space="preserve">Source: sales_analysis_20256.xlsx (sheets "2025" and "2026"), single customer: 160136 SEVEN GEAR FINLAND OY. Aggregated by product CODE; sorted by the absolute size of the change in EUR amount (largest to smallest). Product name (ITEM NAME) sourced from the Uriel catalogs, matched by CODE/SKU - not from the raw sales file.</t>
   </si>
   <si>
     <t xml:space="preserve">Important note: the source file has no date field within the rows, so it cannot be verified from the data itself whether each sheet covers a full calendar year. The 2026 sheet has far fewer rows/units than the 2025 sheet (1,630 units vs 2,980 units), consistent with a partial-year figure (the file was prepared on 14/09/2026) rather than necessarily a real business decline. Verify the exact date range covered by each sheet with Reuven/the user before presenting these numbers as a "decline".</t>
@@ -281,9 +281,6 @@
     <t xml:space="preserve">CODE</t>
   </si>
   <si>
-    <t xml:space="preserve">שם מוצר</t>
-  </si>
-  <si>
     <t xml:space="preserve">ITEM NAME</t>
   </si>
   <si>
@@ -317,537 +314,537 @@
     <t xml:space="preserve">397</t>
   </si>
   <si>
+    <t xml:space="preserve">ANTIBACTERIAL TRAVEL SOCKS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC43D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HINGED KNEE BRACE /ONE SIZE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KNEE SUPPORT/ONE SIZE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THUMB SUPPORT/ONE SIZE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARM SLING POUCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WRIST SUPPORT/ONE SIZE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KNEE SLEEVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUMBO BELT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WRIST SPLINT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICE&amp;GO ELASTIC COLD BANDAGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANKLE SUPPORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUNION + TOE SPREADER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TENNIS BANDAGE/ONE SIZE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELBOW BANDAGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not found in catalogs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANKLE BANDAGE/ONE SIZE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LITTILE TOE BUNION GUARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">379MSP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WINTER KNITTED COTTON HEALTH SOCKS — WHITE/GREY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELBOW SUPPORT/ONE SIZE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">נתוני מקור גולמיים - מקור 2025 (מתוך sales_analysis_20256.xlsx, ללא שינוי)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sale Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item: Name (Grouped)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item: Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item: Display Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount (Net)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount (Foreign Currency)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit price foreign currency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160136 SEVEN GEAR FINLAND OY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266:266 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סד יד דו צדדי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307:307 L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307 L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כרית סיליקון לעקב</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307:307 M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307 M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307:307 XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307 XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-PARENT:35B:35B L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35B L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מגן קרסול שחור</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-PARENT:35B:35B M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35B M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-PARENT:35B:35B S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35B S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-PARENT:35B:35B XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35B XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-PARENT:35B:35B XXL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35B XXL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3641:3641 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3641 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מיישר בוהן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3655:3655 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3655 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שרוול מסיליקון ל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3667:3667 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3667 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מגן בוניון עדין לנעל צרה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3674:3674 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3674 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מ. בוניון + מפריד אצבע</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3675:3675 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3675 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מגן זרת מסיליקון</t>
+  </si>
+  <si>
+    <t xml:space="preserve">379:379MSP-35-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">379MSP-35-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מדרסי ג'ל מולטי ספורט</t>
+  </si>
+  <si>
+    <t xml:space="preserve">379:379MSP-39-42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">379MSP-39-42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">391:391W-39-42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">391W-39-42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גרבי חורף אנטיבקטריאלי לבן</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397:397-35-38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397-35-38</t>
+  </si>
+  <si>
     <t xml:space="preserve">גרבי טיסה</t>
   </si>
   <si>
-    <t xml:space="preserve">Antibacterial travel socks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397A</t>
+    <t xml:space="preserve">397:397-39-42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397-39-42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397:397-43-46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397-43-46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397A:397A-39-42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397A-39-42</t>
   </si>
   <si>
     <t xml:space="preserve">גרבי נסיעות אנטיבקטריאלי</t>
   </si>
   <si>
-    <t xml:space="preserve">AC43D</t>
+    <t xml:space="preserve">45-PARENT:45B:45B L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45B L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מגן ברך שחור</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45-PARENT:45B:45B M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45B M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45-PARENT:45B:45B S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45B S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45-PARENT:45B:45B XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45B XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45-PARENT:45B:45B XXL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45B XXL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78A-PARENT:78A:78A XXL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78A XXL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מגן למפרק כתף</t>
+  </si>
+  <si>
+    <t xml:space="preserve">801:801 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">801 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICE &amp; GO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85-PARENT:85:85 L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85 L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מתלה יד-כיס</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85-PARENT:85:85 M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85 M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85-PARENT:85:85 S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85 S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85-PARENT:85:85 XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85 XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95-PARENT:95B:95B L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95B L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מגן מרפק שחור</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95-PARENT:95B:95B XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95B XL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC07:AC07 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC07 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חגורת גב עם תמיכות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC25:AC25 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC25 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חבק לשורש כף היד</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC27:AC27L 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC27L 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC27:AC27R 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC27R 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC28:AC28 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC28 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">סד לאגודל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC37:AC37 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC37 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מגן קרסול</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC43D:AC43D 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC43D 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מגן ברך + צירים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC45X:AC45X 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC45X 0</t>
   </si>
   <si>
     <t xml:space="preserve">מגן ברך עם תמיכות</t>
   </si>
   <si>
-    <t xml:space="preserve">HINGED KNEE BRACE /ONE SIZE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KNEE SUPPORT/ONE SIZE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סד לאגודל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THUMB SUPPORT/ONE SIZE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מתלה יד-כיס</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARM SLING POUCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חבק לשורש כף היד</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WRIST SUPPORT/ONE SIZE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מגן ברך שחור</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KNEE SLEEVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">חגורת גב עם תמיכות</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUMBO BELT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wrist Splint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICE &amp; GO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ice&amp;Go Elastic Cold Bandage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מגן קרסול שחור</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANKLE SUPPORT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מ. בוניון + מפריד אצבע</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUNION + TOE SPREADER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC91</t>
+    <t xml:space="preserve">AC91:AC91 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC91 0</t>
   </si>
   <si>
     <t xml:space="preserve">חבק טניס</t>
   </si>
   <si>
-    <t xml:space="preserve">TENNIS BANDAGE/ONE SIZE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מגן מרפק שחור</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELBOW BANDAGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מגן בוניון עדין לנעל צרה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not found in catalogs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מגן קרסול</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANKLE BANDAGE/ONE SIZE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">שרוול מסיליקון ל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מגן זרת מסיליקון</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Littile Toe Bunion Guard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">כרית סיליקון לעקב</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312</t>
+    <t xml:space="preserve">AC95:AC95 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC95 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מגן מרפק</t>
+  </si>
+  <si>
+    <t xml:space="preserve">נתוני מקור גולמיים - מקור 2026 (מתוך sales_analysis_20256.xlsx, ללא שינוי)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312:312 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312 0</t>
   </si>
   <si>
     <t xml:space="preserve">מדבקה גדולה מסיליקון</t>
   </si>
   <si>
-    <t xml:space="preserve">266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סד יד דו צדדי</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מיישר בוהן</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מגן למפרק כתף</t>
-  </si>
-  <si>
-    <t xml:space="preserve">379MSP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מדרסי ג'ל מולטי ספורט</t>
-  </si>
-  <si>
-    <t xml:space="preserve">391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">גרבי חורף אנטיבקטריאלי לבן</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Winter Knitted Cotton Health Socks — White/Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מגן מרפק</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELBOW SUPPORT/ONE SIZE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grand Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">נתוני מקור גולמיים - מקור 2025 (מתוך sales_analysis_20256.xlsx, ללא שינוי)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sale Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item: Name (Grouped)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item: Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item: Display Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amount (Net)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amount (Foreign Currency)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit price foreign currency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160136 SEVEN GEAR FINLAND OY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266:266 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307:307 L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307 L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307:307 M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307 M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307:307 XL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307 XL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-PARENT:35B:35B L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35B L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-PARENT:35B:35B M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35B M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-PARENT:35B:35B S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35B S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-PARENT:35B:35B XL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35B XL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-PARENT:35B:35B XXL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35B XXL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3641:3641 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3641 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3655:3655 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3655 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3667:3667 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3667 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3674:3674 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3674 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3675:3675 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3675 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">379:379MSP-35-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">379MSP-35-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">379:379MSP-39-42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">379MSP-39-42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">391:391W-39-42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">391W-39-42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397:397-35-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397-35-38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397:397-39-42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397-39-42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397:397-43-46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397-43-46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397A:397A-39-42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397A-39-42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45-PARENT:45B:45B L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45B L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45-PARENT:45B:45B M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45B M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45-PARENT:45B:45B S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45B S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45-PARENT:45B:45B XL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45B XL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45-PARENT:45B:45B XXL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45B XXL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78A-PARENT:78A:78A XXL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78A XXL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">801:801 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">801 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85-PARENT:85:85 L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85 L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85-PARENT:85:85 M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85 M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85-PARENT:85:85 S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85 S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85-PARENT:85:85 XL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85 XL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95-PARENT:95B:95B L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95B L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95-PARENT:95B:95B XL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95B XL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC07:AC07 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC07 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC25:AC25 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC25 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC27:AC27L 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC27L 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC27:AC27R 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC27R 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC28:AC28 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC28 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC37:AC37 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC37 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC43D:AC43D 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC43D 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מגן ברך + צירים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC45X:AC45X 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC45X 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC91:AC91 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC91 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC95:AC95 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AC95 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">נתוני מקור גולמיים - מקור 2026 (מתוך sales_analysis_20256.xlsx, ללא שינוי)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312:312 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312 0</t>
-  </si>
-  <si>
     <t xml:space="preserve">397A:397A-35-38</t>
   </si>
   <si>
@@ -887,7 +884,7 @@
     <t xml:space="preserve">  - סה"כ קודים שנבדקו (איחוד שתי השנים): 27 קודים ייחודיים.</t>
   </si>
   <si>
-    <t xml:space="preserve">  - סה"כ יחידות 2025: =SUM('השוואה'!D7:D33) יח' | סה"כ יחידות 2026: =SUM('השוואה'!E7:E33) יח' (ראו שורת הסה"כ בגיליון ההשוואה).</t>
+    <t xml:space="preserve">  - סה"כ יחידות 2025: =SUM('השוואה'!C7:C33) יח' | סה"כ יחידות 2026: =SUM('השוואה'!D7:D33) יח' (ראו שורת הסה"כ בגיליון ההשוואה).</t>
   </si>
   <si>
     <t xml:space="preserve">  - סה"כ סכום ביורו 2025: 15,927.49 € | סה"כ סכום ביורו 2026: 9,257.00 € - ירידה של כ-42% במונחים גולמיים.</t>
@@ -914,10 +911,10 @@
     <t xml:space="preserve">הערת שם מוצר:</t>
   </si>
   <si>
-    <t xml:space="preserve">  - CODE AC43D הופיע ב-2025 תחת שני שמות שונים ("מגן ברך + צירים" ו-"מגן ברך עם תמיכות"); נבחר השם עם הכמות הגדולה יותר לייצוג בטבלה (ראו הערה בטור B).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - CODE AC27 מופיע בקובץ המקור ללא שם מוצר תקין (שדה "Item: Display Name" מכיל את הקוד עצמו, "AC27") - כך גם מוצג בטבלה.</t>
+    <t xml:space="preserve">  - CODE AC43D הופיע במקור הגולמי ב-2025 תחת שני שמות שונים בעברית ("מגן ברך + צירים" ו-"מגן ברך עם תמיכות") - פרט זה כבר לא רלוונטי לתצוגה הנוכחית: עמודת שם המוצר בעברית הוסרה מהטבלה, ועמודת ITEM NAME נשלפת מהקטלוג האנגלי לפי CODE ולא מהשדה הזה.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - CODE AC27 מופיע בקובץ המקור ללא שם מוצר תקין בעברית (שדה "Item: Display Name" מכיל את הקוד עצמו, "AC27") - אך עמודת ITEM NAME הנוכחית מציגה "WRIST SPLINT" (נשלף מקטלוג SELECTED, וריאציית SKU ‏AC27L/AC27R, ראו הערת תא בעמודה B).</t>
   </si>
   <si>
     <t xml:space="preserve">העליות והירידות הבולטות ביותר (מוינות לפי גודל השינוי המוחלט בסכום ביורו):</t>
@@ -950,7 +947,7 @@
     <t xml:space="preserve">  - עמודת "Amount (Foreign Currency)" בקובץ המקור היא ביורו (€) - נלקחה כפי שהיא משורות המקור, ללא המרה נוספת (אין צורך בשער חליפין קבוע, הסכום כבר נתון ביורו לכל שורה).</t>
   </si>
   <si>
-    <t xml:space="preserve">  - קוד שמופיע רק באחת השנים מוצג עם 0 בשנה החסרה (לא נעלם ולא מוצג כתא ריק), ועמודת ה-% המתאימה מציגה "מוצר חדש" כדי למנוע חלוקה באפס.</t>
+    <t xml:space="preserve">  - קוד שמופיע רק באחת השנים מוצג עם 0 בשנה החסרה (לא נעלם ולא מוצג כתא ריק), ועמודת ה-% המתאימה מציגה "New product" כדי למנוע חלוקה באפס.</t>
   </si>
   <si>
     <t xml:space="preserve">  - מיון הטבלה בגיליון "השוואה": לפי גודל השינוי המוחלט בסכום ביורו (הגדול ביותר, חיובי או שלילי, קודם) - כלומר השינויים המשמעותיים ביותר עסקית מופיעים למעלה.</t>
@@ -1451,18 +1448,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1497,7 +1493,6 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
@@ -1533,1322 +1528,1237 @@
       <c r="K6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="6" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="8" t="n">
+      <c r="C7" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A7,'מקור 2025'!$J:$J)</f>
         <v>390</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="D7" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A7,'מקור 2026'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="8" t="n">
-        <f aca="false">E7-D7</f>
+      <c r="E7" s="8" t="n">
+        <f aca="false">D7-C7</f>
         <v>-390</v>
       </c>
-      <c r="G7" s="9" t="n">
-        <f aca="false">IF(D7=0,"New product",(E7-D7)/D7)</f>
+      <c r="F7" s="9" t="n">
+        <f aca="false">IF(C7=0,"New product",(D7-C7)/C7)</f>
         <v>-1</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="G7" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A7,'מקור 2025'!$L:$L)</f>
         <v>3159</v>
       </c>
-      <c r="I7" s="10" t="n">
+      <c r="H7" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A7,'מקור 2026'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="10" t="n">
-        <f aca="false">I7-H7</f>
+      <c r="I7" s="10" t="n">
+        <f aca="false">H7-G7</f>
         <v>-3159</v>
       </c>
-      <c r="K7" s="9" t="n">
-        <f aca="false">IF(H7=0,"New product",(I7-H7)/H7)</f>
+      <c r="J7" s="9" t="n">
+        <f aca="false">IF(G7=0,"New product",(H7-G7)/G7)</f>
         <v>-1</v>
       </c>
-      <c r="L7" s="7" t="str">
-        <f aca="false">IF(AND(D7&gt;0,E7=0),"Discontinued in 2026",IF(AND(D7=0,E7&gt;0),"New in 2026",IF(AND(D7&gt;0,D7&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K7" s="7" t="str">
+        <f aca="false">IF(AND(C7&gt;0,D7=0),"Discontinued in 2026",IF(AND(C7=0,D7&gt;0),"New in 2026",IF(AND(C7&gt;0,C7&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>Discontinued in 2026</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A8,'מקור 2025'!$J:$J)</f>
         <v>1</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="D8" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A8,'מקור 2026'!$J:$J)</f>
         <v>370</v>
       </c>
-      <c r="F8" s="8" t="n">
-        <f aca="false">E8-D8</f>
+      <c r="E8" s="8" t="n">
+        <f aca="false">D8-C8</f>
         <v>369</v>
       </c>
-      <c r="G8" s="9" t="n">
-        <f aca="false">IF(D8=0,"New product",(E8-D8)/D8)</f>
+      <c r="F8" s="9" t="n">
+        <f aca="false">IF(C8=0,"New product",(D8-C8)/C8)</f>
         <v>369</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="G8" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A8,'מקור 2025'!$L:$L)</f>
         <v>0.01</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="H8" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A8,'מקור 2026'!$L:$L)</f>
         <v>2997</v>
       </c>
-      <c r="J8" s="10" t="n">
-        <f aca="false">I8-H8</f>
+      <c r="I8" s="10" t="n">
+        <f aca="false">H8-G8</f>
         <v>2996.99</v>
       </c>
-      <c r="K8" s="9" t="n">
-        <f aca="false">IF(H8=0,"New product",(I8-H8)/H8)</f>
+      <c r="J8" s="9" t="n">
+        <f aca="false">IF(G8=0,"New product",(H8-G8)/G8)</f>
         <v>299699</v>
       </c>
-      <c r="L8" s="7" t="str">
-        <f aca="false">IF(AND(D8&gt;0,E8=0),"Discontinued in 2026",IF(AND(D8=0,E8&gt;0),"New in 2026",IF(AND(D8&gt;0,D8&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K8" s="7" t="str">
+        <f aca="false">IF(AND(C8&gt;0,D8=0),"Discontinued in 2026",IF(AND(C8=0,D8&gt;0),"New in 2026",IF(AND(C8&gt;0,C8&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>2025 base negligible (&lt;10 units) - % not informative</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="C9" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A9,'מקור 2025'!$J:$J)</f>
         <v>160</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="D9" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A9,'מקור 2026'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="8" t="n">
-        <f aca="false">E9-D9</f>
+      <c r="E9" s="8" t="n">
+        <f aca="false">D9-C9</f>
         <v>-160</v>
       </c>
-      <c r="G9" s="9" t="n">
-        <f aca="false">IF(D9=0,"New product",(E9-D9)/D9)</f>
+      <c r="F9" s="9" t="n">
+        <f aca="false">IF(C9=0,"New product",(D9-C9)/C9)</f>
         <v>-1</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="G9" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A9,'מקור 2025'!$L:$L)</f>
         <v>1583</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="H9" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A9,'מקור 2026'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="10" t="n">
-        <f aca="false">I9-H9</f>
+      <c r="I9" s="10" t="n">
+        <f aca="false">H9-G9</f>
         <v>-1583</v>
       </c>
-      <c r="K9" s="9" t="n">
-        <f aca="false">IF(H9=0,"New product",(I9-H9)/H9)</f>
+      <c r="J9" s="9" t="n">
+        <f aca="false">IF(G9=0,"New product",(H9-G9)/G9)</f>
         <v>-1</v>
       </c>
-      <c r="L9" s="7" t="str">
-        <f aca="false">IF(AND(D9&gt;0,E9=0),"Discontinued in 2026",IF(AND(D9=0,E9&gt;0),"New in 2026",IF(AND(D9&gt;0,D9&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K9" s="7" t="str">
+        <f aca="false">IF(AND(C9&gt;0,D9=0),"Discontinued in 2026",IF(AND(C9=0,D9&gt;0),"New in 2026",IF(AND(C9&gt;0,C9&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>Discontinued in 2026</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="C10" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A10,'מקור 2025'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="D10" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A10,'מקור 2026'!$J:$J)</f>
         <v>100</v>
       </c>
-      <c r="F10" s="8" t="n">
-        <f aca="false">E10-D10</f>
+      <c r="E10" s="8" t="n">
+        <f aca="false">D10-C10</f>
         <v>100</v>
       </c>
-      <c r="G10" s="9" t="str">
-        <f aca="false">IF(D10=0,"New product",(E10-D10)/D10)</f>
+      <c r="F10" s="9" t="str">
+        <f aca="false">IF(C10=0,"New product",(D10-C10)/C10)</f>
         <v>New product</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="G10" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A10,'מקור 2025'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="H10" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A10,'מקור 2026'!$L:$L)</f>
         <v>955</v>
       </c>
-      <c r="J10" s="10" t="n">
-        <f aca="false">I10-H10</f>
+      <c r="I10" s="10" t="n">
+        <f aca="false">H10-G10</f>
         <v>955</v>
       </c>
-      <c r="K10" s="9" t="str">
-        <f aca="false">IF(H10=0,"New product",(I10-H10)/H10)</f>
+      <c r="J10" s="9" t="str">
+        <f aca="false">IF(G10=0,"New product",(H10-G10)/G10)</f>
         <v>New product</v>
       </c>
-      <c r="L10" s="7" t="str">
-        <f aca="false">IF(AND(D10&gt;0,E10=0),"Discontinued in 2026",IF(AND(D10=0,E10&gt;0),"New in 2026",IF(AND(D10&gt;0,D10&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K10" s="7" t="str">
+        <f aca="false">IF(AND(C10&gt;0,D10=0),"Discontinued in 2026",IF(AND(C10=0,D10&gt;0),"New in 2026",IF(AND(C10&gt;0,C10&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>New in 2026</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C11" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A11,'מקור 2025'!$J:$J)</f>
         <v>470</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="D11" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A11,'מקור 2026'!$J:$J)</f>
         <v>260</v>
       </c>
-      <c r="F11" s="8" t="n">
-        <f aca="false">E11-D11</f>
+      <c r="E11" s="8" t="n">
+        <f aca="false">D11-C11</f>
         <v>-210</v>
       </c>
-      <c r="G11" s="9" t="n">
-        <f aca="false">IF(D11=0,"New product",(E11-D11)/D11)</f>
+      <c r="F11" s="9" t="n">
+        <f aca="false">IF(C11=0,"New product",(D11-C11)/C11)</f>
         <v>-0.446808510638298</v>
       </c>
-      <c r="H11" s="10" t="n">
+      <c r="G11" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A11,'מקור 2025'!$L:$L)</f>
         <v>1997.5</v>
       </c>
-      <c r="I11" s="10" t="n">
+      <c r="H11" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A11,'מקור 2026'!$L:$L)</f>
         <v>1105</v>
       </c>
-      <c r="J11" s="10" t="n">
-        <f aca="false">I11-H11</f>
+      <c r="I11" s="10" t="n">
+        <f aca="false">H11-G11</f>
         <v>-892.5</v>
       </c>
-      <c r="K11" s="9" t="n">
-        <f aca="false">IF(H11=0,"New product",(I11-H11)/H11)</f>
+      <c r="J11" s="9" t="n">
+        <f aca="false">IF(G11=0,"New product",(H11-G11)/G11)</f>
         <v>-0.446808510638298</v>
       </c>
-      <c r="L11" s="7" t="str">
-        <f aca="false">IF(AND(D11&gt;0,E11=0),"Discontinued in 2026",IF(AND(D11=0,E11&gt;0),"New in 2026",IF(AND(D11&gt;0,D11&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K11" s="7" t="str">
+        <f aca="false">IF(AND(C11&gt;0,D11=0),"Discontinued in 2026",IF(AND(C11=0,D11&gt;0),"New in 2026",IF(AND(C11&gt;0,C11&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C12" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A12,'מקור 2025'!$J:$J)</f>
         <v>155</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="D12" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A12,'מקור 2026'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="8" t="n">
-        <f aca="false">E12-D12</f>
+      <c r="E12" s="8" t="n">
+        <f aca="false">D12-C12</f>
         <v>-155</v>
       </c>
-      <c r="G12" s="9" t="n">
-        <f aca="false">IF(D12=0,"New product",(E12-D12)/D12)</f>
+      <c r="F12" s="9" t="n">
+        <f aca="false">IF(C12=0,"New product",(D12-C12)/C12)</f>
         <v>-1</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="G12" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A12,'מקור 2025'!$L:$L)</f>
         <v>852.5</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="H12" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A12,'מקור 2026'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="10" t="n">
-        <f aca="false">I12-H12</f>
+      <c r="I12" s="10" t="n">
+        <f aca="false">H12-G12</f>
         <v>-852.5</v>
       </c>
-      <c r="K12" s="9" t="n">
-        <f aca="false">IF(H12=0,"New product",(I12-H12)/H12)</f>
+      <c r="J12" s="9" t="n">
+        <f aca="false">IF(G12=0,"New product",(H12-G12)/G12)</f>
         <v>-1</v>
       </c>
-      <c r="L12" s="7" t="str">
-        <f aca="false">IF(AND(D12&gt;0,E12=0),"Discontinued in 2026",IF(AND(D12=0,E12&gt;0),"New in 2026",IF(AND(D12&gt;0,D12&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K12" s="7" t="str">
+        <f aca="false">IF(AND(C12&gt;0,D12=0),"Discontinued in 2026",IF(AND(C12=0,D12&gt;0),"New in 2026",IF(AND(C12&gt;0,C12&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>Discontinued in 2026</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="C13" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A13,'מקור 2025'!$J:$J)</f>
         <v>450</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="D13" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A13,'מקור 2026'!$J:$J)</f>
         <v>260</v>
       </c>
-      <c r="F13" s="8" t="n">
-        <f aca="false">E13-D13</f>
+      <c r="E13" s="8" t="n">
+        <f aca="false">D13-C13</f>
         <v>-190</v>
       </c>
-      <c r="G13" s="9" t="n">
-        <f aca="false">IF(D13=0,"New product",(E13-D13)/D13)</f>
+      <c r="F13" s="9" t="n">
+        <f aca="false">IF(C13=0,"New product",(D13-C13)/C13)</f>
         <v>-0.422222222222222</v>
       </c>
-      <c r="H13" s="10" t="n">
+      <c r="G13" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A13,'מקור 2025'!$L:$L)</f>
         <v>1912.5</v>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="H13" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A13,'מקור 2026'!$L:$L)</f>
         <v>1105</v>
       </c>
-      <c r="J13" s="10" t="n">
-        <f aca="false">I13-H13</f>
+      <c r="I13" s="10" t="n">
+        <f aca="false">H13-G13</f>
         <v>-807.5</v>
       </c>
-      <c r="K13" s="9" t="n">
-        <f aca="false">IF(H13=0,"New product",(I13-H13)/H13)</f>
+      <c r="J13" s="9" t="n">
+        <f aca="false">IF(G13=0,"New product",(H13-G13)/G13)</f>
         <v>-0.422222222222222</v>
       </c>
-      <c r="L13" s="7" t="str">
-        <f aca="false">IF(AND(D13&gt;0,E13=0),"Discontinued in 2026",IF(AND(D13=0,E13&gt;0),"New in 2026",IF(AND(D13&gt;0,D13&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K13" s="7" t="str">
+        <f aca="false">IF(AND(C13&gt;0,D13=0),"Discontinued in 2026",IF(AND(C13=0,D13&gt;0),"New in 2026",IF(AND(C13&gt;0,C13&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="C14" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A14,'מקור 2025'!$J:$J)</f>
         <v>255</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="D14" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A14,'מקור 2026'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="8" t="n">
-        <f aca="false">E14-D14</f>
+      <c r="E14" s="8" t="n">
+        <f aca="false">D14-C14</f>
         <v>-255</v>
       </c>
-      <c r="G14" s="9" t="n">
-        <f aca="false">IF(D14=0,"New product",(E14-D14)/D14)</f>
+      <c r="F14" s="9" t="n">
+        <f aca="false">IF(C14=0,"New product",(D14-C14)/C14)</f>
         <v>-1</v>
       </c>
-      <c r="H14" s="10" t="n">
+      <c r="G14" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A14,'מקור 2025'!$L:$L)</f>
         <v>803.25</v>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="H14" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A14,'מקור 2026'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="10" t="n">
-        <f aca="false">I14-H14</f>
+      <c r="I14" s="10" t="n">
+        <f aca="false">H14-G14</f>
         <v>-803.25</v>
       </c>
-      <c r="K14" s="9" t="n">
-        <f aca="false">IF(H14=0,"New product",(I14-H14)/H14)</f>
+      <c r="J14" s="9" t="n">
+        <f aca="false">IF(G14=0,"New product",(H14-G14)/G14)</f>
         <v>-1</v>
       </c>
-      <c r="L14" s="7" t="str">
-        <f aca="false">IF(AND(D14&gt;0,E14=0),"Discontinued in 2026",IF(AND(D14=0,E14&gt;0),"New in 2026",IF(AND(D14&gt;0,D14&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K14" s="7" t="str">
+        <f aca="false">IF(AND(C14&gt;0,D14=0),"Discontinued in 2026",IF(AND(C14=0,D14&gt;0),"New in 2026",IF(AND(C14&gt;0,C14&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>Discontinued in 2026</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="C15" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A15,'מקור 2025'!$J:$J)</f>
         <v>60</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="D15" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A15,'מקור 2026'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="8" t="n">
-        <f aca="false">E15-D15</f>
+      <c r="E15" s="8" t="n">
+        <f aca="false">D15-C15</f>
         <v>-60</v>
       </c>
-      <c r="G15" s="9" t="n">
-        <f aca="false">IF(D15=0,"New product",(E15-D15)/D15)</f>
+      <c r="F15" s="9" t="n">
+        <f aca="false">IF(C15=0,"New product",(D15-C15)/C15)</f>
         <v>-1</v>
       </c>
-      <c r="H15" s="10" t="n">
+      <c r="G15" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A15,'מקור 2025'!$L:$L)</f>
         <v>675</v>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="H15" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A15,'מקור 2026'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="10" t="n">
-        <f aca="false">I15-H15</f>
+      <c r="I15" s="10" t="n">
+        <f aca="false">H15-G15</f>
         <v>-675</v>
       </c>
-      <c r="K15" s="9" t="n">
-        <f aca="false">IF(H15=0,"New product",(I15-H15)/H15)</f>
+      <c r="J15" s="9" t="n">
+        <f aca="false">IF(G15=0,"New product",(H15-G15)/G15)</f>
         <v>-1</v>
       </c>
-      <c r="L15" s="7" t="str">
-        <f aca="false">IF(AND(D15&gt;0,E15=0),"Discontinued in 2026",IF(AND(D15=0,E15&gt;0),"New in 2026",IF(AND(D15&gt;0,D15&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K15" s="7" t="str">
+        <f aca="false">IF(AND(C15&gt;0,D15=0),"Discontinued in 2026",IF(AND(C15=0,D15&gt;0),"New in 2026",IF(AND(C15&gt;0,C15&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>Discontinued in 2026</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="C16" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A16,'מקור 2025'!$J:$J)</f>
         <v>70</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="D16" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A16,'מקור 2026'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="8" t="n">
-        <f aca="false">E16-D16</f>
+      <c r="E16" s="8" t="n">
+        <f aca="false">D16-C16</f>
         <v>-70</v>
       </c>
-      <c r="G16" s="9" t="n">
-        <f aca="false">IF(D16=0,"New product",(E16-D16)/D16)</f>
+      <c r="F16" s="9" t="n">
+        <f aca="false">IF(C16=0,"New product",(D16-C16)/C16)</f>
         <v>-1</v>
       </c>
-      <c r="H16" s="10" t="n">
+      <c r="G16" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A16,'מקור 2025'!$L:$L)</f>
         <v>584.5</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="H16" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A16,'מקור 2026'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="10" t="n">
-        <f aca="false">I16-H16</f>
+      <c r="I16" s="10" t="n">
+        <f aca="false">H16-G16</f>
         <v>-584.5</v>
       </c>
-      <c r="K16" s="9" t="n">
-        <f aca="false">IF(H16=0,"New product",(I16-H16)/H16)</f>
+      <c r="J16" s="9" t="n">
+        <f aca="false">IF(G16=0,"New product",(H16-G16)/G16)</f>
         <v>-1</v>
       </c>
-      <c r="L16" s="7" t="str">
-        <f aca="false">IF(AND(D16&gt;0,E16=0),"Discontinued in 2026",IF(AND(D16=0,E16&gt;0),"New in 2026",IF(AND(D16&gt;0,D16&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K16" s="7" t="str">
+        <f aca="false">IF(AND(C16&gt;0,D16=0),"Discontinued in 2026",IF(AND(C16=0,D16&gt;0),"New in 2026",IF(AND(C16&gt;0,C16&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>Discontinued in 2026</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="C17" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A17,'מקור 2025'!$J:$J)</f>
         <v>130</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="D17" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A17,'מקור 2026'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="8" t="n">
-        <f aca="false">E17-D17</f>
+      <c r="E17" s="8" t="n">
+        <f aca="false">D17-C17</f>
         <v>-130</v>
       </c>
-      <c r="G17" s="9" t="n">
-        <f aca="false">IF(D17=0,"New product",(E17-D17)/D17)</f>
+      <c r="F17" s="9" t="n">
+        <f aca="false">IF(C17=0,"New product",(D17-C17)/C17)</f>
         <v>-1</v>
       </c>
-      <c r="H17" s="10" t="n">
+      <c r="G17" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A17,'מקור 2025'!$L:$L)</f>
         <v>364</v>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="H17" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A17,'מקור 2026'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="10" t="n">
-        <f aca="false">I17-H17</f>
+      <c r="I17" s="10" t="n">
+        <f aca="false">H17-G17</f>
         <v>-364</v>
       </c>
-      <c r="K17" s="9" t="n">
-        <f aca="false">IF(H17=0,"New product",(I17-H17)/H17)</f>
+      <c r="J17" s="9" t="n">
+        <f aca="false">IF(G17=0,"New product",(H17-G17)/G17)</f>
         <v>-1</v>
       </c>
-      <c r="L17" s="7" t="str">
-        <f aca="false">IF(AND(D17&gt;0,E17=0),"Discontinued in 2026",IF(AND(D17=0,E17&gt;0),"New in 2026",IF(AND(D17&gt;0,D17&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K17" s="7" t="str">
+        <f aca="false">IF(AND(C17&gt;0,D17=0),"Discontinued in 2026",IF(AND(C17=0,D17&gt;0),"New in 2026",IF(AND(C17&gt;0,C17&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>Discontinued in 2026</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="C18" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A18,'מקור 2025'!$J:$J)</f>
         <v>155</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="D18" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A18,'מקור 2026'!$J:$J)</f>
         <v>60</v>
       </c>
-      <c r="F18" s="8" t="n">
-        <f aca="false">E18-D18</f>
+      <c r="E18" s="8" t="n">
+        <f aca="false">D18-C18</f>
         <v>-95</v>
       </c>
-      <c r="G18" s="9" t="n">
-        <f aca="false">IF(D18=0,"New product",(E18-D18)/D18)</f>
+      <c r="F18" s="9" t="n">
+        <f aca="false">IF(C18=0,"New product",(D18-C18)/C18)</f>
         <v>-0.612903225806452</v>
       </c>
-      <c r="H18" s="10" t="n">
+      <c r="G18" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A18,'מקור 2025'!$L:$L)</f>
         <v>480.5</v>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="H18" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A18,'מקור 2026'!$L:$L)</f>
         <v>186</v>
       </c>
-      <c r="J18" s="10" t="n">
-        <f aca="false">I18-H18</f>
+      <c r="I18" s="10" t="n">
+        <f aca="false">H18-G18</f>
         <v>-294.5</v>
       </c>
-      <c r="K18" s="9" t="n">
-        <f aca="false">IF(H18=0,"New product",(I18-H18)/H18)</f>
+      <c r="J18" s="9" t="n">
+        <f aca="false">IF(G18=0,"New product",(H18-G18)/G18)</f>
         <v>-0.612903225806452</v>
       </c>
-      <c r="L18" s="7" t="str">
-        <f aca="false">IF(AND(D18&gt;0,E18=0),"Discontinued in 2026",IF(AND(D18=0,E18&gt;0),"New in 2026",IF(AND(D18&gt;0,D18&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K18" s="7" t="str">
+        <f aca="false">IF(AND(C18&gt;0,D18=0),"Discontinued in 2026",IF(AND(C18=0,D18&gt;0),"New in 2026",IF(AND(C18&gt;0,C18&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="C19" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A19,'מקור 2025'!$J:$J)</f>
         <v>140</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="D19" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A19,'מקור 2026'!$J:$J)</f>
         <v>80</v>
       </c>
-      <c r="F19" s="8" t="n">
-        <f aca="false">E19-D19</f>
+      <c r="E19" s="8" t="n">
+        <f aca="false">D19-C19</f>
         <v>-60</v>
       </c>
-      <c r="G19" s="9" t="n">
-        <f aca="false">IF(D19=0,"New product",(E19-D19)/D19)</f>
+      <c r="F19" s="9" t="n">
+        <f aca="false">IF(C19=0,"New product",(D19-C19)/C19)</f>
         <v>-0.428571428571429</v>
       </c>
-      <c r="H19" s="10" t="n">
+      <c r="G19" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A19,'מקור 2025'!$L:$L)</f>
         <v>651</v>
       </c>
-      <c r="I19" s="10" t="n">
+      <c r="H19" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A19,'מקור 2026'!$L:$L)</f>
         <v>372</v>
       </c>
-      <c r="J19" s="10" t="n">
-        <f aca="false">I19-H19</f>
+      <c r="I19" s="10" t="n">
+        <f aca="false">H19-G19</f>
         <v>-279</v>
       </c>
-      <c r="K19" s="9" t="n">
-        <f aca="false">IF(H19=0,"New product",(I19-H19)/H19)</f>
+      <c r="J19" s="9" t="n">
+        <f aca="false">IF(G19=0,"New product",(H19-G19)/G19)</f>
         <v>-0.428571428571429</v>
       </c>
-      <c r="L19" s="7" t="str">
-        <f aca="false">IF(AND(D19&gt;0,E19=0),"Discontinued in 2026",IF(AND(D19=0,E19&gt;0),"New in 2026",IF(AND(D19&gt;0,D19&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K19" s="7" t="str">
+        <f aca="false">IF(AND(C19&gt;0,D19=0),"Discontinued in 2026",IF(AND(C19=0,D19&gt;0),"New in 2026",IF(AND(C19&gt;0,C19&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="C20" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A20,'מקור 2025'!$J:$J)</f>
         <v>70</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="D20" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A20,'מקור 2026'!$J:$J)</f>
         <v>20</v>
       </c>
-      <c r="F20" s="8" t="n">
-        <f aca="false">E20-D20</f>
+      <c r="E20" s="8" t="n">
+        <f aca="false">D20-C20</f>
         <v>-50</v>
       </c>
-      <c r="G20" s="9" t="n">
-        <f aca="false">IF(D20=0,"New product",(E20-D20)/D20)</f>
+      <c r="F20" s="9" t="n">
+        <f aca="false">IF(C20=0,"New product",(D20-C20)/C20)</f>
         <v>-0.714285714285714</v>
       </c>
-      <c r="H20" s="10" t="n">
+      <c r="G20" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A20,'מקור 2025'!$L:$L)</f>
         <v>311.5</v>
       </c>
-      <c r="I20" s="10" t="n">
+      <c r="H20" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A20,'מקור 2026'!$L:$L)</f>
         <v>89</v>
       </c>
-      <c r="J20" s="10" t="n">
-        <f aca="false">I20-H20</f>
+      <c r="I20" s="10" t="n">
+        <f aca="false">H20-G20</f>
         <v>-222.5</v>
       </c>
-      <c r="K20" s="9" t="n">
-        <f aca="false">IF(H20=0,"New product",(I20-H20)/H20)</f>
+      <c r="J20" s="9" t="n">
+        <f aca="false">IF(G20=0,"New product",(H20-G20)/G20)</f>
         <v>-0.714285714285714</v>
       </c>
-      <c r="L20" s="7" t="str">
-        <f aca="false">IF(AND(D20&gt;0,E20=0),"Discontinued in 2026",IF(AND(D20=0,E20&gt;0),"New in 2026",IF(AND(D20&gt;0,D20&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K20" s="7" t="str">
+        <f aca="false">IF(AND(C20&gt;0,D20=0),"Discontinued in 2026",IF(AND(C20=0,D20&gt;0),"New in 2026",IF(AND(C20&gt;0,C20&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="C21" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A21,'מקור 2025'!$J:$J)</f>
         <v>20</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="D21" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A21,'מקור 2026'!$J:$J)</f>
         <v>80</v>
       </c>
-      <c r="F21" s="8" t="n">
-        <f aca="false">E21-D21</f>
+      <c r="E21" s="8" t="n">
+        <f aca="false">D21-C21</f>
         <v>60</v>
       </c>
-      <c r="G21" s="9" t="n">
-        <f aca="false">IF(D21=0,"New product",(E21-D21)/D21)</f>
+      <c r="F21" s="9" t="n">
+        <f aca="false">IF(C21=0,"New product",(D21-C21)/C21)</f>
         <v>3</v>
       </c>
-      <c r="H21" s="10" t="n">
+      <c r="G21" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A21,'מקור 2025'!$L:$L)</f>
         <v>62</v>
       </c>
-      <c r="I21" s="10" t="n">
+      <c r="H21" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A21,'מקור 2026'!$L:$L)</f>
         <v>248</v>
       </c>
-      <c r="J21" s="10" t="n">
-        <f aca="false">I21-H21</f>
+      <c r="I21" s="10" t="n">
+        <f aca="false">H21-G21</f>
         <v>186</v>
       </c>
-      <c r="K21" s="9" t="n">
-        <f aca="false">IF(H21=0,"New product",(I21-H21)/H21)</f>
+      <c r="J21" s="9" t="n">
+        <f aca="false">IF(G21=0,"New product",(H21-G21)/G21)</f>
         <v>3</v>
       </c>
-      <c r="L21" s="7" t="str">
-        <f aca="false">IF(AND(D21&gt;0,E21=0),"Discontinued in 2026",IF(AND(D21=0,E21&gt;0),"New in 2026",IF(AND(D21&gt;0,D21&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K21" s="7" t="str">
+        <f aca="false">IF(AND(C21&gt;0,D21=0),"Discontinued in 2026",IF(AND(C21=0,D21&gt;0),"New in 2026",IF(AND(C21&gt;0,C21&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A22,'מקור 2025'!$J:$J)</f>
         <v>40</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="D22" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A22,'מקור 2026'!$J:$J)</f>
         <v>80</v>
       </c>
-      <c r="F22" s="8" t="n">
-        <f aca="false">E22-D22</f>
+      <c r="E22" s="8" t="n">
+        <f aca="false">D22-C22</f>
         <v>40</v>
       </c>
-      <c r="G22" s="9" t="n">
-        <f aca="false">IF(D22=0,"New product",(E22-D22)/D22)</f>
+      <c r="F22" s="9" t="n">
+        <f aca="false">IF(C22=0,"New product",(D22-C22)/C22)</f>
         <v>1</v>
       </c>
-      <c r="H22" s="10" t="n">
+      <c r="G22" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A22,'מקור 2025'!$L:$L)</f>
         <v>182</v>
       </c>
-      <c r="I22" s="10" t="n">
+      <c r="H22" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A22,'מקור 2026'!$L:$L)</f>
         <v>364</v>
       </c>
-      <c r="J22" s="10" t="n">
-        <f aca="false">I22-H22</f>
+      <c r="I22" s="10" t="n">
+        <f aca="false">H22-G22</f>
         <v>182</v>
       </c>
-      <c r="K22" s="9" t="n">
-        <f aca="false">IF(H22=0,"New product",(I22-H22)/H22)</f>
+      <c r="J22" s="9" t="n">
+        <f aca="false">IF(G22=0,"New product",(H22-G22)/G22)</f>
         <v>1</v>
       </c>
-      <c r="L22" s="7" t="str">
-        <f aca="false">IF(AND(D22&gt;0,E22=0),"Discontinued in 2026",IF(AND(D22=0,E22&gt;0),"New in 2026",IF(AND(D22&gt;0,D22&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K22" s="7" t="str">
+        <f aca="false">IF(AND(C22&gt;0,D22=0),"Discontinued in 2026",IF(AND(C22=0,D22&gt;0),"New in 2026",IF(AND(C22&gt;0,C22&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="C23" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A23,'מקור 2025'!$J:$J)</f>
         <v>30</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="D23" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A23,'מקור 2026'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="8" t="n">
-        <f aca="false">E23-D23</f>
+      <c r="E23" s="8" t="n">
+        <f aca="false">D23-C23</f>
         <v>-30</v>
       </c>
-      <c r="G23" s="9" t="n">
-        <f aca="false">IF(D23=0,"New product",(E23-D23)/D23)</f>
+      <c r="F23" s="9" t="n">
+        <f aca="false">IF(C23=0,"New product",(D23-C23)/C23)</f>
         <v>-1</v>
       </c>
-      <c r="H23" s="10" t="n">
+      <c r="G23" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A23,'מקור 2025'!$L:$L)</f>
         <v>157.5</v>
       </c>
-      <c r="I23" s="10" t="n">
+      <c r="H23" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A23,'מקור 2026'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="10" t="n">
-        <f aca="false">I23-H23</f>
+      <c r="I23" s="10" t="n">
+        <f aca="false">H23-G23</f>
         <v>-157.5</v>
       </c>
-      <c r="K23" s="9" t="n">
-        <f aca="false">IF(H23=0,"New product",(I23-H23)/H23)</f>
+      <c r="J23" s="9" t="n">
+        <f aca="false">IF(G23=0,"New product",(H23-G23)/G23)</f>
         <v>-1</v>
       </c>
-      <c r="L23" s="7" t="str">
-        <f aca="false">IF(AND(D23&gt;0,E23=0),"Discontinued in 2026",IF(AND(D23=0,E23&gt;0),"New in 2026",IF(AND(D23&gt;0,D23&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K23" s="7" t="str">
+        <f aca="false">IF(AND(C23&gt;0,D23=0),"Discontinued in 2026",IF(AND(C23=0,D23&gt;0),"New in 2026",IF(AND(C23&gt;0,C23&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>Discontinued in 2026</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A24,'מקור 2025'!$J:$J)</f>
         <v>80</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="D24" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A24,'מקור 2026'!$J:$J)</f>
         <v>40</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <f aca="false">E24-D24</f>
+      <c r="E24" s="8" t="n">
+        <f aca="false">D24-C24</f>
         <v>-40</v>
       </c>
-      <c r="G24" s="9" t="n">
-        <f aca="false">IF(D24=0,"New product",(E24-D24)/D24)</f>
+      <c r="F24" s="9" t="n">
+        <f aca="false">IF(C24=0,"New product",(D24-C24)/C24)</f>
         <v>-0.5</v>
       </c>
-      <c r="H24" s="10" t="n">
+      <c r="G24" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A24,'מקור 2025'!$L:$L)</f>
         <v>304</v>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="H24" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A24,'מקור 2026'!$L:$L)</f>
         <v>152</v>
       </c>
-      <c r="J24" s="10" t="n">
-        <f aca="false">I24-H24</f>
+      <c r="I24" s="10" t="n">
+        <f aca="false">H24-G24</f>
         <v>-152</v>
       </c>
-      <c r="K24" s="9" t="n">
-        <f aca="false">IF(H24=0,"New product",(I24-H24)/H24)</f>
+      <c r="J24" s="9" t="n">
+        <f aca="false">IF(G24=0,"New product",(H24-G24)/G24)</f>
         <v>-0.5</v>
       </c>
-      <c r="L24" s="7" t="str">
-        <f aca="false">IF(AND(D24&gt;0,E24=0),"Discontinued in 2026",IF(AND(D24=0,E24&gt;0),"New in 2026",IF(AND(D24&gt;0,D24&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K24" s="7" t="str">
+        <f aca="false">IF(AND(C24&gt;0,D24=0),"Discontinued in 2026",IF(AND(C24=0,D24&gt;0),"New in 2026",IF(AND(C24&gt;0,C24&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C25" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A25,'מקור 2025'!$J:$J)</f>
         <v>80</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="D25" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A25,'מקור 2026'!$J:$J)</f>
         <v>40</v>
       </c>
-      <c r="F25" s="8" t="n">
-        <f aca="false">E25-D25</f>
+      <c r="E25" s="8" t="n">
+        <f aca="false">D25-C25</f>
         <v>-40</v>
       </c>
-      <c r="G25" s="9" t="n">
-        <f aca="false">IF(D25=0,"New product",(E25-D25)/D25)</f>
+      <c r="F25" s="9" t="n">
+        <f aca="false">IF(C25=0,"New product",(D25-C25)/C25)</f>
         <v>-0.5</v>
       </c>
-      <c r="H25" s="10" t="n">
+      <c r="G25" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A25,'מקור 2025'!$L:$L)</f>
         <v>304</v>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="H25" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A25,'מקור 2026'!$L:$L)</f>
         <v>152</v>
       </c>
-      <c r="J25" s="10" t="n">
-        <f aca="false">I25-H25</f>
+      <c r="I25" s="10" t="n">
+        <f aca="false">H25-G25</f>
         <v>-152</v>
       </c>
-      <c r="K25" s="9" t="n">
-        <f aca="false">IF(H25=0,"New product",(I25-H25)/H25)</f>
+      <c r="J25" s="9" t="n">
+        <f aca="false">IF(G25=0,"New product",(H25-G25)/G25)</f>
         <v>-0.5</v>
       </c>
-      <c r="L25" s="7" t="str">
-        <f aca="false">IF(AND(D25&gt;0,E25=0),"Discontinued in 2026",IF(AND(D25=0,E25&gt;0),"New in 2026",IF(AND(D25&gt;0,D25&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K25" s="7" t="str">
+        <f aca="false">IF(AND(C25&gt;0,D25=0),"Discontinued in 2026",IF(AND(C25=0,D25&gt;0),"New in 2026",IF(AND(C25&gt;0,C25&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A26,'מקור 2025'!$J:$J)</f>
         <v>70</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="D26" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A26,'מקור 2026'!$J:$J)</f>
         <v>60</v>
       </c>
-      <c r="F26" s="8" t="n">
-        <f aca="false">E26-D26</f>
+      <c r="E26" s="8" t="n">
+        <f aca="false">D26-C26</f>
         <v>-10</v>
       </c>
-      <c r="G26" s="9" t="n">
-        <f aca="false">IF(D26=0,"New product",(E26-D26)/D26)</f>
+      <c r="F26" s="9" t="n">
+        <f aca="false">IF(C26=0,"New product",(D26-C26)/C26)</f>
         <v>-0.142857142857143</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="G26" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A26,'מקור 2025'!$L:$L)</f>
         <v>710.5</v>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="H26" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A26,'מקור 2026'!$L:$L)</f>
         <v>609</v>
       </c>
-      <c r="J26" s="10" t="n">
-        <f aca="false">I26-H26</f>
+      <c r="I26" s="10" t="n">
+        <f aca="false">H26-G26</f>
         <v>-101.5</v>
       </c>
-      <c r="K26" s="9" t="n">
-        <f aca="false">IF(H26=0,"New product",(I26-H26)/H26)</f>
+      <c r="J26" s="9" t="n">
+        <f aca="false">IF(G26=0,"New product",(H26-G26)/G26)</f>
         <v>-0.142857142857143</v>
       </c>
-      <c r="L26" s="7" t="str">
-        <f aca="false">IF(AND(D26&gt;0,E26=0),"Discontinued in 2026",IF(AND(D26=0,E26&gt;0),"New in 2026",IF(AND(D26&gt;0,D26&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K26" s="7" t="str">
+        <f aca="false">IF(AND(C26&gt;0,D26=0),"Discontinued in 2026",IF(AND(C26=0,D26&gt;0),"New in 2026",IF(AND(C26&gt;0,C26&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A27,'מקור 2025'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="D27" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A27,'מקור 2026'!$J:$J)</f>
         <v>40</v>
       </c>
-      <c r="F27" s="8" t="n">
-        <f aca="false">E27-D27</f>
+      <c r="E27" s="8" t="n">
+        <f aca="false">D27-C27</f>
         <v>40</v>
       </c>
-      <c r="G27" s="9" t="str">
-        <f aca="false">IF(D27=0,"New product",(E27-D27)/D27)</f>
+      <c r="F27" s="9" t="str">
+        <f aca="false">IF(C27=0,"New product",(D27-C27)/C27)</f>
         <v>New product</v>
       </c>
-      <c r="H27" s="10" t="n">
+      <c r="G27" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A27,'מקור 2025'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="H27" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A27,'מקור 2026'!$L:$L)</f>
         <v>74</v>
       </c>
-      <c r="J27" s="10" t="n">
-        <f aca="false">I27-H27</f>
+      <c r="I27" s="10" t="n">
+        <f aca="false">H27-G27</f>
         <v>74</v>
       </c>
-      <c r="K27" s="9" t="str">
-        <f aca="false">IF(H27=0,"New product",(I27-H27)/H27)</f>
+      <c r="J27" s="9" t="str">
+        <f aca="false">IF(G27=0,"New product",(H27-G27)/G27)</f>
         <v>New product</v>
       </c>
-      <c r="L27" s="7" t="str">
-        <f aca="false">IF(AND(D27&gt;0,E27=0),"Discontinued in 2026",IF(AND(D27=0,E27&gt;0),"New in 2026",IF(AND(D27&gt;0,D27&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K27" s="7" t="str">
+        <f aca="false">IF(AND(C27&gt;0,D27=0),"Discontinued in 2026",IF(AND(C27=0,D27&gt;0),"New in 2026",IF(AND(C27&gt;0,C27&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>New in 2026</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A28,'מקור 2025'!$J:$J)</f>
         <v>110</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="D28" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A28,'מקור 2026'!$J:$J)</f>
         <v>120</v>
       </c>
-      <c r="F28" s="8" t="n">
-        <f aca="false">E28-D28</f>
+      <c r="E28" s="8" t="n">
+        <f aca="false">D28-C28</f>
         <v>10</v>
       </c>
-      <c r="G28" s="9" t="n">
-        <f aca="false">IF(D28=0,"New product",(E28-D28)/D28)</f>
+      <c r="F28" s="9" t="n">
+        <f aca="false">IF(C28=0,"New product",(D28-C28)/C28)</f>
         <v>0.0909090909090909</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="G28" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A28,'מקור 2025'!$L:$L)</f>
         <v>693</v>
       </c>
-      <c r="I28" s="10" t="n">
+      <c r="H28" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A28,'מקור 2026'!$L:$L)</f>
         <v>756</v>
       </c>
-      <c r="J28" s="10" t="n">
-        <f aca="false">I28-H28</f>
+      <c r="I28" s="10" t="n">
+        <f aca="false">H28-G28</f>
         <v>63</v>
       </c>
-      <c r="K28" s="9" t="n">
-        <f aca="false">IF(H28=0,"New product",(I28-H28)/H28)</f>
+      <c r="J28" s="9" t="n">
+        <f aca="false">IF(G28=0,"New product",(H28-G28)/G28)</f>
         <v>0.0909090909090909</v>
       </c>
-      <c r="L28" s="7" t="str">
-        <f aca="false">IF(AND(D28&gt;0,E28=0),"Discontinued in 2026",IF(AND(D28=0,E28&gt;0),"New in 2026",IF(AND(D28&gt;0,D28&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K28" s="7" t="str">
+        <f aca="false">IF(AND(C28&gt;0,D28=0),"Discontinued in 2026",IF(AND(C28=0,D28&gt;0),"New in 2026",IF(AND(C28&gt;0,C28&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A29,'מקור 2025'!$J:$J)</f>
         <v>20</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="D29" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A29,'מקור 2026'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="8" t="n">
-        <f aca="false">E29-D29</f>
+      <c r="E29" s="8" t="n">
+        <f aca="false">D29-C29</f>
         <v>-20</v>
       </c>
-      <c r="G29" s="9" t="n">
-        <f aca="false">IF(D29=0,"New product",(E29-D29)/D29)</f>
+      <c r="F29" s="9" t="n">
+        <f aca="false">IF(C29=0,"New product",(D29-C29)/C29)</f>
         <v>-1</v>
       </c>
-      <c r="H29" s="10" t="n">
+      <c r="G29" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A29,'מקור 2025'!$L:$L)</f>
         <v>30</v>
       </c>
-      <c r="I29" s="10" t="n">
+      <c r="H29" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A29,'מקור 2026'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="10" t="n">
-        <f aca="false">I29-H29</f>
+      <c r="I29" s="10" t="n">
+        <f aca="false">H29-G29</f>
         <v>-30</v>
       </c>
-      <c r="K29" s="9" t="n">
-        <f aca="false">IF(H29=0,"New product",(I29-H29)/H29)</f>
+      <c r="J29" s="9" t="n">
+        <f aca="false">IF(G29=0,"New product",(H29-G29)/G29)</f>
         <v>-1</v>
       </c>
-      <c r="L29" s="7" t="str">
-        <f aca="false">IF(AND(D29&gt;0,E29=0),"Discontinued in 2026",IF(AND(D29=0,E29&gt;0),"New in 2026",IF(AND(D29&gt;0,D29&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K29" s="7" t="str">
+        <f aca="false">IF(AND(C29&gt;0,D29=0),"Discontinued in 2026",IF(AND(C29=0,D29&gt;0),"New in 2026",IF(AND(C29&gt;0,C29&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>Discontinued in 2026</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A30,'מקור 2025'!$J:$J)</f>
         <v>1</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="D30" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A30,'מקור 2026'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="8" t="n">
-        <f aca="false">E30-D30</f>
+      <c r="E30" s="8" t="n">
+        <f aca="false">D30-C30</f>
         <v>-1</v>
       </c>
-      <c r="G30" s="9" t="n">
-        <f aca="false">IF(D30=0,"New product",(E30-D30)/D30)</f>
+      <c r="F30" s="9" t="n">
+        <f aca="false">IF(C30=0,"New product",(D30-C30)/C30)</f>
         <v>-1</v>
       </c>
-      <c r="H30" s="10" t="n">
+      <c r="G30" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A30,'מקור 2025'!$L:$L)</f>
         <v>17.2</v>
       </c>
-      <c r="I30" s="10" t="n">
+      <c r="H30" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A30,'מקור 2026'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="10" t="n">
-        <f aca="false">I30-H30</f>
+      <c r="I30" s="10" t="n">
+        <f aca="false">H30-G30</f>
         <v>-17.2</v>
       </c>
-      <c r="K30" s="9" t="n">
-        <f aca="false">IF(H30=0,"New product",(I30-H30)/H30)</f>
+      <c r="J30" s="9" t="n">
+        <f aca="false">IF(G30=0,"New product",(H30-G30)/G30)</f>
         <v>-1</v>
       </c>
-      <c r="L30" s="7" t="str">
-        <f aca="false">IF(AND(D30&gt;0,E30=0),"Discontinued in 2026",IF(AND(D30=0,E30&gt;0),"New in 2026",IF(AND(D30&gt;0,D30&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K30" s="7" t="str">
+        <f aca="false">IF(AND(C30&gt;0,D30=0),"Discontinued in 2026",IF(AND(C30=0,D30&gt;0),"New in 2026",IF(AND(C30&gt;0,C30&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>Discontinued in 2026</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A31,'מקור 2025'!$J:$J)</f>
         <v>2</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="D31" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A31,'מקור 2026'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="F31" s="8" t="n">
-        <f aca="false">E31-D31</f>
+      <c r="E31" s="8" t="n">
+        <f aca="false">D31-C31</f>
         <v>-2</v>
       </c>
-      <c r="G31" s="9" t="n">
-        <f aca="false">IF(D31=0,"New product",(E31-D31)/D31)</f>
+      <c r="F31" s="9" t="n">
+        <f aca="false">IF(C31=0,"New product",(D31-C31)/C31)</f>
         <v>-1</v>
       </c>
-      <c r="H31" s="10" t="n">
+      <c r="G31" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A31,'מקור 2025'!$L:$L)</f>
         <v>0.02</v>
       </c>
-      <c r="I31" s="10" t="n">
+      <c r="H31" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A31,'מקור 2026'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="10" t="n">
-        <f aca="false">I31-H31</f>
+      <c r="I31" s="10" t="n">
+        <f aca="false">H31-G31</f>
         <v>-0.02</v>
       </c>
-      <c r="K31" s="9" t="n">
-        <f aca="false">IF(H31=0,"New product",(I31-H31)/H31)</f>
+      <c r="J31" s="9" t="n">
+        <f aca="false">IF(G31=0,"New product",(H31-G31)/G31)</f>
         <v>-1</v>
       </c>
-      <c r="L31" s="7" t="str">
-        <f aca="false">IF(AND(D31&gt;0,E31=0),"Discontinued in 2026",IF(AND(D31=0,E31&gt;0),"New in 2026",IF(AND(D31&gt;0,D31&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K31" s="7" t="str">
+        <f aca="false">IF(AND(C31&gt;0,D31=0),"Discontinued in 2026",IF(AND(C31=0,D31&gt;0),"New in 2026",IF(AND(C31&gt;0,C31&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>Discontinued in 2026</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="C32" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A32,'מקור 2025'!$J:$J)</f>
         <v>1</v>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="D32" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A32,'מקור 2026'!$J:$J)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="8" t="n">
-        <f aca="false">E32-D32</f>
+      <c r="E32" s="8" t="n">
+        <f aca="false">D32-C32</f>
         <v>-1</v>
       </c>
-      <c r="G32" s="9" t="n">
-        <f aca="false">IF(D32=0,"New product",(E32-D32)/D32)</f>
+      <c r="F32" s="9" t="n">
+        <f aca="false">IF(C32=0,"New product",(D32-C32)/C32)</f>
         <v>-1</v>
       </c>
-      <c r="H32" s="10" t="n">
+      <c r="G32" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A32,'מקור 2025'!$L:$L)</f>
         <v>0.01</v>
       </c>
-      <c r="I32" s="10" t="n">
+      <c r="H32" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A32,'מקור 2026'!$L:$L)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="10" t="n">
-        <f aca="false">I32-H32</f>
+      <c r="I32" s="10" t="n">
+        <f aca="false">H32-G32</f>
         <v>-0.01</v>
       </c>
-      <c r="K32" s="9" t="n">
-        <f aca="false">IF(H32=0,"New product",(I32-H32)/H32)</f>
+      <c r="J32" s="9" t="n">
+        <f aca="false">IF(G32=0,"New product",(H32-G32)/G32)</f>
         <v>-1</v>
       </c>
-      <c r="L32" s="7" t="str">
-        <f aca="false">IF(AND(D32&gt;0,E32=0),"Discontinued in 2026",IF(AND(D32=0,E32&gt;0),"New in 2026",IF(AND(D32&gt;0,D32&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K32" s="7" t="str">
+        <f aca="false">IF(AND(C32&gt;0,D32=0),"Discontinued in 2026",IF(AND(C32=0,D32&gt;0),"New in 2026",IF(AND(C32&gt;0,C32&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v>Discontinued in 2026</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="C33" s="8" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A33,'מקור 2025'!$J:$J)</f>
         <v>20</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="D33" s="8" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A33,'מקור 2026'!$J:$J)</f>
         <v>20</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <f aca="false">E33-D33</f>
+      <c r="E33" s="8" t="n">
+        <f aca="false">D33-C33</f>
         <v>0</v>
       </c>
-      <c r="G33" s="9" t="n">
-        <f aca="false">IF(D33=0,"New product",(E33-D33)/D33)</f>
+      <c r="F33" s="9" t="n">
+        <f aca="false">IF(C33=0,"New product",(D33-C33)/C33)</f>
         <v>0</v>
       </c>
-      <c r="H33" s="10" t="n">
+      <c r="G33" s="10" t="n">
         <f aca="false">SUMIF('מקור 2025'!$D:$D,$A33,'מקור 2025'!$L:$L)</f>
         <v>93</v>
       </c>
-      <c r="I33" s="10" t="n">
+      <c r="H33" s="10" t="n">
         <f aca="false">SUMIF('מקור 2026'!$D:$D,$A33,'מקור 2026'!$L:$L)</f>
         <v>93</v>
       </c>
-      <c r="J33" s="10" t="n">
-        <f aca="false">I33-H33</f>
+      <c r="I33" s="10" t="n">
+        <f aca="false">H33-G33</f>
         <v>0</v>
       </c>
-      <c r="K33" s="9" t="n">
-        <f aca="false">IF(H33=0,"New product",(I33-H33)/H33)</f>
+      <c r="J33" s="9" t="n">
+        <f aca="false">IF(G33=0,"New product",(H33-G33)/G33)</f>
         <v>0</v>
       </c>
-      <c r="L33" s="7" t="str">
-        <f aca="false">IF(AND(D33&gt;0,E33=0),"Discontinued in 2026",IF(AND(D33=0,E33&gt;0),"New in 2026",IF(AND(D33&gt;0,D33&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
+      <c r="K33" s="7" t="str">
+        <f aca="false">IF(AND(C33&gt;0,D33=0),"Discontinued in 2026",IF(AND(C33=0,D33&gt;0),"New in 2026",IF(AND(C33&gt;0,C33&lt;10),"2025 base negligible (&lt;10 units) - % not informative","")))</f>
         <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
+      <c r="C34" s="13" t="n">
+        <f aca="false">SUM(C7:C33)</f>
+        <v>2980</v>
+      </c>
       <c r="D34" s="13" t="n">
         <f aca="false">SUM(D7:D33)</f>
-        <v>2980</v>
+        <v>1630</v>
       </c>
       <c r="E34" s="13" t="n">
-        <f aca="false">SUM(E7:E33)</f>
-        <v>1630</v>
-      </c>
-      <c r="F34" s="13" t="n">
-        <f aca="false">E34-D34</f>
+        <f aca="false">D34-C34</f>
         <v>-1350</v>
       </c>
-      <c r="G34" s="14" t="n">
-        <f aca="false">IF(D34=0,"",(E34-D34)/D34)</f>
+      <c r="F34" s="14" t="n">
+        <f aca="false">IF(C34=0,"",(D34-C34)/C34)</f>
         <v>-0.453020134228188</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <f aca="false">SUM(G7:G33)</f>
+        <v>15927.49</v>
       </c>
       <c r="H34" s="15" t="n">
         <f aca="false">SUM(H7:H33)</f>
-        <v>15927.49</v>
+        <v>9257</v>
       </c>
       <c r="I34" s="15" t="n">
-        <f aca="false">SUM(I7:I33)</f>
-        <v>9257</v>
-      </c>
-      <c r="J34" s="15" t="n">
-        <f aca="false">I34-H34</f>
+        <f aca="false">H34-G34</f>
         <v>-6670.49</v>
       </c>
-      <c r="K34" s="14" t="n">
-        <f aca="false">IF(H34=0,"",(I34-H34)/H34)</f>
+      <c r="J34" s="14" t="n">
+        <f aca="false">IF(G34=0,"",(H34-G34)/G34)</f>
         <v>-0.418803590521796</v>
       </c>
-      <c r="L34" s="12"/>
+      <c r="K34" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A4:K4"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2886,48 +2796,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2935,19 +2845,19 @@
         <v>160136</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H3" s="16" t="n">
         <v>23.28606</v>
@@ -2973,19 +2883,19 @@
         <v>160136</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H4" s="16" t="n">
         <v>25.20756</v>
@@ -3011,19 +2921,19 @@
         <v>160136</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H5" s="16" t="n">
         <v>23.93496</v>
@@ -3049,19 +2959,19 @@
         <v>160136</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H6" s="16" t="n">
         <v>38.56188</v>
@@ -3087,19 +2997,19 @@
         <v>160136</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H7" s="16" t="n">
         <v>40.61218</v>
@@ -3125,19 +3035,19 @@
         <v>160136</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H8" s="16" t="n">
         <v>38.56188</v>
@@ -3163,19 +3073,19 @@
         <v>160136</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H9" s="16" t="n">
         <v>38.56188</v>
@@ -3201,19 +3111,19 @@
         <v>160136</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H10" s="16" t="n">
         <v>11.77752</v>
@@ -3239,19 +3149,19 @@
         <v>160136</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H11" s="16" t="n">
         <v>11.45822</v>
@@ -3277,19 +3187,19 @@
         <v>160136</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H12" s="16" t="n">
         <v>11.45822</v>
@@ -3315,19 +3225,19 @@
         <v>160136</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H13" s="16" t="n">
         <v>11.77752</v>
@@ -3353,19 +3263,19 @@
         <v>160136</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H14" s="16" t="n">
         <v>11.77752</v>
@@ -3391,19 +3301,19 @@
         <v>160136</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H15" s="16" t="n">
         <v>11.45822</v>
@@ -3429,19 +3339,19 @@
         <v>160136</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H16" s="16" t="n">
         <v>11.77752</v>
@@ -3467,19 +3377,19 @@
         <v>160136</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H17" s="16" t="n">
         <v>11.45822</v>
@@ -3505,19 +3415,19 @@
         <v>160136</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H18" s="16" t="n">
         <v>12.40372</v>
@@ -3543,19 +3453,19 @@
         <v>160136</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H19" s="16" t="n">
         <v>11.45822</v>
@@ -3581,19 +3491,19 @@
         <v>160136</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="H20" s="16" t="n">
         <v>5.5443</v>
@@ -3619,19 +3529,19 @@
         <v>160136</v>
       </c>
       <c r="C21" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D21" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>123</v>
-      </c>
       <c r="G21" s="16" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="H21" s="16" t="n">
         <v>14.04556</v>
@@ -3657,19 +3567,19 @@
         <v>160136</v>
       </c>
       <c r="C22" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>123</v>
-      </c>
       <c r="G22" s="16" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="H22" s="16" t="n">
         <v>15.20456</v>
@@ -3695,19 +3605,19 @@
         <v>160136</v>
       </c>
       <c r="C23" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>123</v>
-      </c>
       <c r="G23" s="16" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="H23" s="16" t="n">
         <v>14.43696</v>
@@ -3733,19 +3643,19 @@
         <v>160136</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="H24" s="16" t="n">
         <v>16.81771</v>
@@ -3771,19 +3681,19 @@
         <v>160136</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="H25" s="16" t="n">
         <v>18.60558</v>
@@ -3809,19 +3719,19 @@
         <v>160136</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="H26" s="16" t="n">
         <v>17.18733</v>
@@ -3847,19 +3757,19 @@
         <v>160136</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="H27" s="16" t="n">
         <v>17.66628</v>
@@ -3885,19 +3795,19 @@
         <v>160136</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="H28" s="16" t="n">
         <v>14.43696</v>
@@ -3923,19 +3833,19 @@
         <v>160136</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="H29" s="16" t="n">
         <v>14.04556</v>
@@ -3961,19 +3871,19 @@
         <v>160136</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="H30" s="16" t="n">
         <v>15.20456</v>
@@ -3999,19 +3909,19 @@
         <v>160136</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H31" s="16" t="n">
         <v>0.040012</v>
@@ -4037,19 +3947,19 @@
         <v>160136</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H32" s="16" t="n">
         <v>0.040012</v>
@@ -4075,19 +3985,19 @@
         <v>160136</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="H33" s="16" t="n">
         <v>0.037519</v>
@@ -4113,19 +4023,19 @@
         <v>160136</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="H34" s="16" t="n">
         <v>30.77352</v>
@@ -4151,19 +4061,19 @@
         <v>160136</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="H35" s="16" t="n">
         <v>29.93922</v>
@@ -4189,19 +4099,19 @@
         <v>160136</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="H36" s="16" t="n">
         <v>32.40972</v>
@@ -4227,19 +4137,19 @@
         <v>160136</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="H37" s="16" t="n">
         <v>32.40972</v>
@@ -4265,19 +4175,19 @@
         <v>160136</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="H38" s="16" t="n">
         <v>30.77352</v>
@@ -4303,19 +4213,19 @@
         <v>160136</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="H39" s="16" t="n">
         <v>29.93922</v>
@@ -4341,19 +4251,19 @@
         <v>160136</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="H40" s="16" t="n">
         <v>29.93922</v>
@@ -4379,19 +4289,19 @@
         <v>160136</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="H41" s="16" t="n">
         <v>32.40972</v>
@@ -4417,19 +4327,19 @@
         <v>160136</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="H42" s="16" t="n">
         <v>30.77352</v>
@@ -4455,19 +4365,19 @@
         <v>160136</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="H43" s="16" t="n">
         <v>0.037519</v>
@@ -4493,19 +4403,19 @@
         <v>160136</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="H44" s="16" t="n">
         <v>11.64303</v>
@@ -4531,19 +4441,19 @@
         <v>160136</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="H45" s="16" t="n">
         <v>11.96748</v>
@@ -4569,19 +4479,19 @@
         <v>160136</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="H46" s="16" t="n">
         <v>11.64303</v>
@@ -4607,19 +4517,19 @@
         <v>160136</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="H47" s="16" t="n">
         <v>11.96748</v>
@@ -4645,19 +4555,19 @@
         <v>160136</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="H48" s="16" t="n">
         <v>11.96748</v>
@@ -4683,19 +4593,19 @@
         <v>160136</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="H49" s="16" t="n">
         <v>11.64303</v>
@@ -4721,19 +4631,19 @@
         <v>160136</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="H50" s="16" t="n">
         <v>11.96748</v>
@@ -4759,19 +4669,19 @@
         <v>160136</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="G51" s="16" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="H51" s="16" t="n">
         <v>12.60378</v>
@@ -4797,19 +4707,19 @@
         <v>160136</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="H52" s="16" t="n">
         <v>11.96748</v>
@@ -4835,19 +4745,19 @@
         <v>160136</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="G53" s="16" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="H53" s="16" t="n">
         <v>11.64303</v>
@@ -4873,19 +4783,19 @@
         <v>160136</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="H54" s="16" t="n">
         <v>65.34624</v>
@@ -4911,19 +4821,19 @@
         <v>160136</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="H55" s="16" t="n">
         <v>10.63776</v>
@@ -4949,19 +4859,19 @@
         <v>160136</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="H56" s="16" t="n">
         <v>22.0066</v>
@@ -4987,19 +4897,19 @@
         <v>160136</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G57" s="16" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="H57" s="16" t="n">
         <v>20.3291</v>
@@ -5025,19 +4935,19 @@
         <v>160136</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="H58" s="16" t="n">
         <v>22.0066</v>
@@ -5063,19 +4973,19 @@
         <v>160136</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="H59" s="16" t="n">
         <v>20.3291</v>
@@ -5101,19 +5011,19 @@
         <v>160136</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="H60" s="16" t="n">
         <v>22.0066</v>
@@ -5139,19 +5049,19 @@
         <v>160136</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="H61" s="16" t="n">
         <v>20.3291</v>
@@ -5177,19 +5087,19 @@
         <v>160136</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="H62" s="16" t="n">
         <v>20.3291</v>
@@ -5215,19 +5125,19 @@
         <v>160136</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="G63" s="16" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="H63" s="16" t="n">
         <v>11.45822</v>
@@ -5253,19 +5163,19 @@
         <v>160136</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="H64" s="16" t="n">
         <v>11.77752</v>
@@ -5291,19 +5201,19 @@
         <v>160136</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>39</v>
+        <v>163</v>
       </c>
       <c r="H65" s="16" t="n">
         <v>41.58225</v>
@@ -5329,19 +5239,19 @@
         <v>160136</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>39</v>
+        <v>163</v>
       </c>
       <c r="H66" s="16" t="n">
         <v>45.0135</v>
@@ -5367,19 +5277,19 @@
         <v>160136</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>39</v>
+        <v>163</v>
       </c>
       <c r="H67" s="16" t="n">
         <v>42.741</v>
@@ -5405,19 +5315,19 @@
         <v>160136</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="H68" s="16" t="n">
         <v>17.0051</v>
@@ -5443,19 +5353,19 @@
         <v>160136</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F69" s="16" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G69" s="16" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="H69" s="16" t="n">
         <v>16.1466</v>
@@ -5481,19 +5391,19 @@
         <v>160136</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="H70" s="16" t="n">
         <v>15.70885</v>
@@ -5519,19 +5429,19 @@
         <v>160136</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F71" s="16" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="G71" s="16" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H71" s="16" t="n">
         <v>31.72332</v>
@@ -5557,19 +5467,19 @@
         <v>160136</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H72" s="16" t="n">
         <v>30.86327</v>
@@ -5595,19 +5505,19 @@
         <v>160136</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F73" s="16" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="G73" s="16" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H73" s="16" t="n">
         <v>31.72332</v>
@@ -5633,19 +5543,19 @@
         <v>160136</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H74" s="16" t="n">
         <v>30.86327</v>
@@ -5671,19 +5581,19 @@
         <v>160136</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E75" s="16" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="H75" s="16" t="n">
         <v>15.70885</v>
@@ -5709,19 +5619,19 @@
         <v>160136</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="H76" s="16" t="n">
         <v>16.1466</v>
@@ -5747,19 +5657,19 @@
         <v>160136</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="H77" s="16" t="n">
         <v>17.0051</v>
@@ -5785,19 +5695,19 @@
         <v>160136</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>62</v>
+        <v>176</v>
       </c>
       <c r="H78" s="16" t="n">
         <v>19.9458</v>
@@ -5823,19 +5733,19 @@
         <v>160136</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E79" s="16" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F79" s="16" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G79" s="16" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H79" s="16" t="n">
         <v>49.21476</v>
@@ -5861,19 +5771,19 @@
         <v>160136</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F80" s="16" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H80" s="16" t="n">
         <v>46.73016</v>
@@ -5899,19 +5809,19 @@
         <v>160136</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F81" s="16" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G81" s="16" t="s">
-        <v>22</v>
+        <v>182</v>
       </c>
       <c r="H81" s="16" t="n">
         <v>35.29871</v>
@@ -5937,19 +5847,19 @@
         <v>160136</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F82" s="16" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>22</v>
+        <v>182</v>
       </c>
       <c r="H82" s="16" t="n">
         <v>36.28236</v>
@@ -5975,19 +5885,19 @@
         <v>160136</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F83" s="16" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G83" s="16" t="s">
-        <v>22</v>
+        <v>182</v>
       </c>
       <c r="H83" s="16" t="n">
         <v>38.21146</v>
@@ -6013,19 +5923,19 @@
         <v>160136</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="H84" s="16" t="n">
         <v>16.44809</v>
@@ -6051,19 +5961,19 @@
         <v>160136</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G85" s="16" t="s">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="H85" s="16" t="n">
         <v>17.80534</v>
@@ -6089,19 +5999,19 @@
         <v>160136</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="H86" s="16" t="n">
         <v>16.90644</v>
@@ -6127,19 +6037,19 @@
         <v>160136</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G87" s="16" t="s">
-        <v>85</v>
+        <v>188</v>
       </c>
       <c r="H87" s="16" t="n">
         <v>17.66628</v>
@@ -6165,19 +6075,19 @@
         <v>160136</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>85</v>
+        <v>188</v>
       </c>
       <c r="H88" s="16" t="n">
         <v>17.18733</v>
@@ -6234,48 +6144,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6283,19 +6193,19 @@
         <v>160136</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H3" s="16" t="n">
         <v>22.68441</v>
@@ -6321,19 +6231,19 @@
         <v>160136</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H4" s="16" t="n">
         <v>22.03236</v>
@@ -6359,19 +6269,19 @@
         <v>160136</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H5" s="16" t="n">
         <v>36.547105</v>
@@ -6397,19 +6307,19 @@
         <v>160136</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H6" s="16" t="n">
         <v>35.49658</v>
@@ -6435,19 +6345,19 @@
         <v>160136</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H7" s="16" t="n">
         <v>35.49658</v>
@@ -6473,19 +6383,19 @@
         <v>160136</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H8" s="16" t="n">
         <v>36.547105</v>
@@ -6511,19 +6421,19 @@
         <v>160136</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E9" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>192</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>72</v>
       </c>
       <c r="H9" s="16" t="n">
         <v>6.46982</v>
@@ -6549,19 +6459,19 @@
         <v>160136</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="E10" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="G10" s="16" t="s">
         <v>192</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>72</v>
       </c>
       <c r="H10" s="16" t="n">
         <v>6.661295</v>
@@ -6587,19 +6497,19 @@
         <v>160136</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H11" s="16" t="n">
         <v>11.16217</v>
@@ -6625,19 +6535,19 @@
         <v>160136</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H12" s="16" t="n">
         <v>10.84132</v>
@@ -6663,19 +6573,19 @@
         <v>160136</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H13" s="16" t="n">
         <v>10.84132</v>
@@ -6701,19 +6611,19 @@
         <v>160136</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H14" s="16" t="n">
         <v>11.16217</v>
@@ -6739,19 +6649,19 @@
         <v>160136</v>
       </c>
       <c r="C15" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>123</v>
-      </c>
       <c r="G15" s="16" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="H15" s="16" t="n">
         <v>13.28936</v>
@@ -6777,19 +6687,19 @@
         <v>160136</v>
       </c>
       <c r="C16" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>123</v>
-      </c>
       <c r="G16" s="16" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="H16" s="16" t="n">
         <v>13.68266</v>
@@ -6815,19 +6725,19 @@
         <v>160136</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="H17" s="16" t="n">
         <v>16.383185</v>
@@ -6853,19 +6763,19 @@
         <v>160136</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="H18" s="16" t="n">
         <v>15.91226</v>
@@ -6891,19 +6801,19 @@
         <v>160136</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="H19" s="16" t="n">
         <v>16.26198</v>
@@ -6929,19 +6839,19 @@
         <v>160136</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="H20" s="16" t="n">
         <v>16.743255</v>
@@ -6967,19 +6877,19 @@
         <v>160136</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="H21" s="16" t="n">
         <v>13.68266</v>
@@ -7005,19 +6915,19 @@
         <v>160136</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="H22" s="16" t="n">
         <v>13.28936</v>
@@ -7043,19 +6953,19 @@
         <v>160136</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E23" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="F23" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="F23" s="16" t="s">
-        <v>195</v>
-      </c>
       <c r="G23" s="16" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="H23" s="16" t="n">
         <v>29.16567</v>
@@ -7081,19 +6991,19 @@
         <v>160136</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E24" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="F24" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="F24" s="16" t="s">
-        <v>195</v>
-      </c>
       <c r="G24" s="16" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="H24" s="16" t="n">
         <v>28.32732</v>
@@ -7119,19 +7029,19 @@
         <v>160136</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="H25" s="16" t="n">
         <v>29.16567</v>
@@ -7157,19 +7067,19 @@
         <v>160136</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="H26" s="16" t="n">
         <v>28.32732</v>
@@ -7195,19 +7105,19 @@
         <v>160136</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E27" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="F27" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="F27" s="16" t="s">
-        <v>197</v>
-      </c>
       <c r="G27" s="16" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="H27" s="16" t="n">
         <v>28.32732</v>
@@ -7233,19 +7143,19 @@
         <v>160136</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E28" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="F28" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="F28" s="16" t="s">
-        <v>197</v>
-      </c>
       <c r="G28" s="16" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="H28" s="16" t="n">
         <v>29.16567</v>
@@ -7271,19 +7181,19 @@
         <v>160136</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="H29" s="16" t="n">
         <v>10.84132</v>
@@ -7309,19 +7219,19 @@
         <v>160136</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="H30" s="16" t="n">
         <v>11.16217</v>
@@ -7347,19 +7257,19 @@
         <v>160136</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E31" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="F31" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="F31" s="16" t="s">
-        <v>199</v>
-      </c>
       <c r="G31" s="16" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="H31" s="16" t="n">
         <v>11.16217</v>
@@ -7385,19 +7295,19 @@
         <v>160136</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E32" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="F32" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="F32" s="16" t="s">
-        <v>199</v>
-      </c>
       <c r="G32" s="16" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="H32" s="16" t="n">
         <v>10.84132</v>
@@ -7423,19 +7333,19 @@
         <v>160136</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="H33" s="16" t="n">
         <v>10.84132</v>
@@ -7461,19 +7371,19 @@
         <v>160136</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="H34" s="16" t="n">
         <v>11.16217</v>
@@ -7499,19 +7409,19 @@
         <v>160136</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="H35" s="16" t="n">
         <v>15.302975</v>
@@ -7537,19 +7447,19 @@
         <v>160136</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
       <c r="H36" s="16" t="n">
         <v>14.8631</v>
@@ -7575,19 +7485,19 @@
         <v>160136</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="H37" s="16" t="n">
         <v>15.302975</v>
@@ -7613,19 +7523,19 @@
         <v>160136</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="H38" s="16" t="n">
         <v>14.8631</v>
@@ -7651,19 +7561,19 @@
         <v>160136</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>22</v>
+        <v>182</v>
       </c>
       <c r="H39" s="16" t="n">
         <v>34.386685</v>
@@ -7689,19 +7599,19 @@
         <v>160136</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>22</v>
+        <v>182</v>
       </c>
       <c r="H40" s="16" t="n">
         <v>33.39826</v>
@@ -7727,19 +7637,19 @@
         <v>160136</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="H41" s="16" t="n">
         <v>16.023115</v>
@@ -7765,19 +7675,19 @@
         <v>160136</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="H42" s="16" t="n">
         <v>15.56254</v>
@@ -7803,19 +7713,19 @@
         <v>160136</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>85</v>
+        <v>188</v>
       </c>
       <c r="H43" s="16" t="n">
         <v>16.743255</v>
@@ -7841,19 +7751,19 @@
         <v>160136</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>85</v>
+        <v>188</v>
       </c>
       <c r="H44" s="16" t="n">
         <v>16.26198</v>
@@ -7898,12 +7808,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B2" s="19" t="n">
         <f aca="false">השוואה!B2</f>
@@ -7912,37 +7822,37 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7950,12 +7860,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7963,22 +7873,22 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7986,17 +7896,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8004,17 +7914,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8022,22 +7932,22 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8045,32 +7955,32 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
